--- a/output/pdf_financials_xlsx/HEM.xlsx
+++ b/output/pdf_financials_xlsx/HEM.xlsx
@@ -15208,7 +15208,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HEM.xlsx
+++ b/output/pdf_financials_xlsx/HEM.xlsx
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000923</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0017</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.086309</v>
+        <v>-0.085386</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.077741</v>
+        <v>-0.076041</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-7.947387</v>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.086309</v>
+        <v>-0.085386</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.077741</v>
+        <v>-0.076041</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-7.947387</v>
@@ -2121,22 +2121,22 @@
         <v>1.471038</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.024064</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.219445</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.135746</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.155416</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.7057</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.682117</v>
       </c>
     </row>
     <row r="35">
@@ -2213,22 +2213,22 @@
         <v>1.471038</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.024064</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.219445</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.135746</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.155416</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.7057</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.682117</v>
       </c>
     </row>
     <row r="37">
@@ -2765,22 +2765,22 @@
         <v>0.088242</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.037381</v>
+        <v>0.013317</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.445445</v>
+        <v>0.226</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.326</v>
+        <v>0.190254</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.288522</v>
+        <v>0.133106</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.962175</v>
+        <v>0.256475</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.810008</v>
+        <v>0.127891</v>
       </c>
     </row>
     <row r="49">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -31944,7 +31944,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -32961,7 +32961,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -33601,7 +33601,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -40891,7 +40891,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
